--- a/testakten/sozialrecht-rollstuhl-tannenberg/Fristen_Familie_Tannenberg.xlsx
+++ b/testakten/sozialrecht-rollstuhl-tannenberg/Fristen_Familie_Tannenberg.xlsx
@@ -487,7 +487,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kanzlei RA Helge Holm, Forstweg 11, 24105 Kiel - Stand 22. Mai 2026</t>
+          <t>Kanzlei Holm · Petersen · Sönnichsen, RA Lasse Holm, Holstenstraße 124, 24103 Kiel - Stand 22. Mai 2026</t>
         </is>
       </c>
     </row>

--- a/testakten/sozialrecht-rollstuhl-tannenberg/Fristen_Familie_Tannenberg.xlsx
+++ b/testakten/sozialrecht-rollstuhl-tannenberg/Fristen_Familie_Tannenberg.xlsx
@@ -480,7 +480,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fristenuebersicht Familie Tannenberg - alle 4 Verfahren</t>
+          <t>Fristenübersicht Familie Tannenberg - alle 4 Verfahren</t>
         </is>
       </c>
     </row>
@@ -491,6 +491,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -504,7 +505,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Behoerde / Gericht</t>
+          <t>Behörde / Gericht</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -583,7 +584,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Eilantrag wegen Versorgungsluecke</t>
+          <t>Eilantrag wegen Versorgungslücke</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -709,7 +710,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Pflegegrad-Hoeherstufung 3 auf 4 SGB XI</t>
+          <t>Pflegegrad-Höherstufung 3 auf 4 SGB XI</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -756,7 +757,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>DRV Nord Luebeck</t>
+          <t>DRV Nord Lübeck</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -855,10 +856,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Verfahrensverlauf - chronologische Sicht ueber alle vier Verfahren</t>
-        </is>
-      </c>
-    </row>
+          <t>Verfahrensverlauf - chronologische Sicht über alle vier Verfahren</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -882,7 +884,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Konsequenz / naechster Schritt</t>
+          <t>Konsequenz / nächster Schritt</t>
         </is>
       </c>
     </row>
@@ -909,7 +911,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Anlage zu spaeterem Widerspruch</t>
+          <t>Anlage zu späterem Widerspruch</t>
         </is>
       </c>
     </row>
@@ -931,12 +933,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Fachaerztliche Stellungnahme</t>
+          <t>Fachärztliche Stellungnahme</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Hauptbegruendung</t>
+          <t>Hauptbegründung</t>
         </is>
       </c>
     </row>
@@ -953,7 +955,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Dr. Brunsbuettel DRV</t>
+          <t>Dr. Brunsbüttel DRV</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -963,7 +965,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>spaeter Grundlage fuer Ablehnung</t>
+          <t>später Grundlage für Ablehnung</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1041,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Hausaerztl. Stellungnahme</t>
+          <t>Hausärztl. Stellungnahme</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Hauptbegruendung Widerspruch</t>
+          <t>Hauptbegründung Widerspruch</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1068,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Bescheid - Hoeherstufung abgelehnt</t>
+          <t>Bescheid - Höherstufung abgelehnt</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1098,7 +1100,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Hauptbegruendung</t>
+          <t>Hauptbegründung</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1117,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>DRV Nord Luebeck</t>
+          <t>DRV Nord Lübeck</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1174,7 +1176,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Erstgespraech, Mandat</t>
+          <t>Erstgespräch, Mandat</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
